--- a/ig/DM-DECEMBRE-2025/ValueSet-JDV-J198-FonctionLieu-ROR.xlsx
+++ b/ig/DM-DECEMBRE-2025/ValueSet-JDV-J198-FonctionLieu-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="87">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251017120000</t>
+    <t>20251222120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-17T12:00:00+01:00</t>
+    <t>2025-12-22T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -181,6 +181,90 @@
   </si>
   <si>
     <t>Bloc obstétrical</t>
+  </si>
+  <si>
+    <t>015</t>
+  </si>
+  <si>
+    <t>Local de cabinet de ville d'ergothérapie</t>
+  </si>
+  <si>
+    <t>016</t>
+  </si>
+  <si>
+    <t>Local de cabinet de ville de diététique</t>
+  </si>
+  <si>
+    <t>017</t>
+  </si>
+  <si>
+    <t>Local de cabinet dentaire ou de stomatologie</t>
+  </si>
+  <si>
+    <t>018</t>
+  </si>
+  <si>
+    <t>Local de cabinet de ville de kinésithérapie</t>
+  </si>
+  <si>
+    <t>019</t>
+  </si>
+  <si>
+    <t>Local de cabinet de ville infirmier</t>
+  </si>
+  <si>
+    <t>020</t>
+  </si>
+  <si>
+    <t>Local de cabinet de ville de maïeutique</t>
+  </si>
+  <si>
+    <t>021</t>
+  </si>
+  <si>
+    <t>Local de cabinet de ville d’oto-rhino-laryngologie (ORL)</t>
+  </si>
+  <si>
+    <t>022</t>
+  </si>
+  <si>
+    <t>Local de cabinet de ville de cardiologie</t>
+  </si>
+  <si>
+    <t>023</t>
+  </si>
+  <si>
+    <t>Local de cabinet de ville de médecine générale</t>
+  </si>
+  <si>
+    <t>024</t>
+  </si>
+  <si>
+    <t>Local de cabinet de ville de Médecine Physique et de Réadaptation (MPR)</t>
+  </si>
+  <si>
+    <t>025</t>
+  </si>
+  <si>
+    <t>Local de cabinet de ville de rhumatologie</t>
+  </si>
+  <si>
+    <t>026</t>
+  </si>
+  <si>
+    <t>Local de cabinet de ville de pédiatrie</t>
+  </si>
+  <si>
+    <t>027</t>
+  </si>
+  <si>
+    <t>Local de cabinet de ville d’ophtalmologie</t>
+  </si>
+  <si>
+    <t>028</t>
+  </si>
+  <si>
+    <t>Local de cabinet de ville de pneumologie</t>
   </si>
   <si>
     <t/>
@@ -451,7 +535,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -583,15 +667,127 @@
         <v>56</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>86</v>
       </c>
     </row>
   </sheetData>
